--- a/output/tables/AF_cancer/tabla1_AF_2016.xlsx
+++ b/output/tables/AF_cancer/tabla1_AF_2016.xlsx
@@ -367,17 +367,17 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>**General (N=4493)**</t>
+          <t>**General (N=5093)**</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>**No family history (N=3381)**</t>
+          <t>**No family history (N=3832)**</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>**≥1 relative with cancer (N=1112)**</t>
+          <t>**≥1 relative with cancer (N=1261)**</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -394,22 +394,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>11,239,720</t>
+          <t>11,285,215</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>48.2 (15.5)</t>
+          <t>48.1 (15.6)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>47.2 (15.6)</t>
+          <t>47.2 (15.7)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>51.5 (14.7)</t>
+          <t>51.2 (14.8)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -426,7 +426,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>11,239,720</t>
+          <t>11,285,215</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -443,17 +443,17 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1,525 (47.5%)</t>
+          <t>1,768 (47.4%)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1,240 (50.6%)</t>
+          <t>1,437 (50.4%)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>285 (36.7%)</t>
+          <t>331 (37.1%)</t>
         </is>
       </c>
     </row>
@@ -465,17 +465,17 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1,731 (37.2%)</t>
+          <t>1,937 (37.2%)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1,226 (34.8%)</t>
+          <t>1,372 (34.8%)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>505 (45.3%)</t>
+          <t>565 (45.2%)</t>
         </is>
       </c>
     </row>
@@ -487,17 +487,17 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1,237 (15.3%)</t>
+          <t>1,388 (15.4%)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>915 (14.6%)</t>
+          <t>1,023 (14.7%)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>322 (18.0%)</t>
+          <t>365 (17.7%)</t>
         </is>
       </c>
     </row>
@@ -509,12 +509,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>11,239,720</t>
+          <t>11,285,215</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.4</t>
         </is>
       </c>
     </row>
@@ -526,17 +526,17 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1,628 (49.2%)</t>
+          <t>1,876 (49.1%)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1,264 (49.6%)</t>
+          <t>1,460 (49.7%)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>364 (47.6%)</t>
+          <t>416 (47.0%)</t>
         </is>
       </c>
     </row>
@@ -548,17 +548,17 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2,865 (50.8%)</t>
+          <t>3,217 (50.9%)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2,117 (50.4%)</t>
+          <t>2,372 (50.3%)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>748 (52.4%)</t>
+          <t>845 (53.0%)</t>
         </is>
       </c>
     </row>
@@ -570,12 +570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>11,165,226</t>
+          <t>11,205,097</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>0.083</t>
         </is>
       </c>
     </row>
@@ -587,17 +587,17 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1,210 (19.1%)</t>
+          <t>1,349 (18.8%)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>895 (18.0%)</t>
+          <t>997 (17.9%)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>315 (23.0%)</t>
+          <t>352 (22.0%)</t>
         </is>
       </c>
     </row>
@@ -609,17 +609,17 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2,342 (54.0%)</t>
+          <t>2,648 (53.9%)</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1,744 (53.9%)</t>
+          <t>1,974 (53.8%)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>598 (54.1%)</t>
+          <t>674 (54.3%)</t>
         </is>
       </c>
     </row>
@@ -631,17 +631,17 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>900 (26.9%)</t>
+          <t>1,044 (27.2%)</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>713 (28.1%)</t>
+          <t>825 (28.3%)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>187 (22.9%)</t>
+          <t>219 (23.6%)</t>
         </is>
       </c>
     </row>
@@ -653,12 +653,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11,239,720</t>
+          <t>11,285,215</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.10</t>
         </is>
       </c>
     </row>
@@ -670,17 +670,17 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3,746 (88.9%)</t>
+          <t>4,253 (89.1%)</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2,786 (88.6%)</t>
+          <t>3,164 (88.6%)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>960 (90.1%)</t>
+          <t>1,089 (90.7%)</t>
         </is>
       </c>
     </row>
@@ -692,17 +692,17 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>747 (11.1%)</t>
+          <t>840 (10.9%)</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>595 (11.4%)</t>
+          <t>668 (11.4%)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>152 (9.9%)</t>
+          <t>172 (9.3%)</t>
         </is>
       </c>
     </row>
@@ -714,12 +714,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11,239,720</t>
+          <t>11,285,215</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
@@ -731,17 +731,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3,219 (66.4%)</t>
+          <t>3,653 (66.4%)</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2,395 (65.9%)</t>
+          <t>2,722 (65.8%)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>824 (68.3%)</t>
+          <t>931 (68.6%)</t>
         </is>
       </c>
     </row>
@@ -753,17 +753,17 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1,274 (33.6%)</t>
+          <t>1,440 (33.6%)</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>986 (34.1%)</t>
+          <t>1,110 (34.2%)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>288 (31.7%)</t>
+          <t>330 (31.4%)</t>
         </is>
       </c>
     </row>
@@ -775,12 +775,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>11,179,123</t>
+          <t>9,973,111</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>28 (0.6%)</t>
+          <t>28 (0.7%)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -814,17 +814,17 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>890 (18.8%)</t>
+          <t>890 (18.7%)</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>669 (17.9%)</t>
+          <t>669 (17.7%)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>221 (22.0%)</t>
+          <t>221 (22.3%)</t>
         </is>
       </c>
     </row>
@@ -836,17 +836,17 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1,757 (42.4%)</t>
+          <t>1,757 (42.5%)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1,328 (43.2%)</t>
+          <t>1,328 (43.5%)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>429 (39.5%)</t>
+          <t>429 (39.0%)</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>452 (37.6%)</t>
+          <t>452 (37.9%)</t>
         </is>
       </c>
     </row>
@@ -880,12 +880,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>10,879,802</t>
+          <t>10,934,782</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.5</t>
         </is>
       </c>
     </row>
@@ -897,17 +897,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1,839 (35.4%)</t>
+          <t>2,089 (35.6%)</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1,414 (36.1%)</t>
+          <t>1,598 (36.2%)</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>425 (33.3%)</t>
+          <t>491 (33.6%)</t>
         </is>
       </c>
     </row>
@@ -919,17 +919,17 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>974 (24.7%)</t>
+          <t>1,105 (24.1%)</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>711 (23.7%)</t>
+          <t>807 (23.4%)</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>263 (28.1%)</t>
+          <t>298 (26.4%)</t>
         </is>
       </c>
     </row>
@@ -941,17 +941,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1,523 (39.9%)</t>
+          <t>1,725 (40.3%)</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1,139 (40.2%)</t>
+          <t>1,296 (40.4%)</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>384 (38.6%)</t>
+          <t>429 (40.1%)</t>
         </is>
       </c>
     </row>
@@ -963,27 +963,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>11,237,487</t>
+          <t>10,023,207</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>383 (12.3%)</t>
+          <t>383 (12.0%)</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>308 (12.4%)</t>
+          <t>308 (12.1%)</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>75 (11.6%)</t>
+          <t>75 (11.5%)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.8</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>11,239,720</t>
+          <t>11,285,215</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.070</t>
+          <t>0.10</t>
         </is>
       </c>
     </row>
@@ -1012,17 +1012,17 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4,420 (98.9%)</t>
+          <t>5,007 (98.7%)</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3,329 (99.2%)</t>
+          <t>3,771 (99.0%)</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1,091 (97.8%)</t>
+          <t>1,236 (97.8%)</t>
         </is>
       </c>
     </row>
@@ -1034,17 +1034,17 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>73 (1.1%)</t>
+          <t>86 (1.3%)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>52 (0.8%)</t>
+          <t>61 (1.0%)</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>21 (2.2%)</t>
+          <t>25 (2.2%)</t>
         </is>
       </c>
     </row>
